--- a/quizzes/028_kitchen_task_assessment_form--quizzes.xlsx
+++ b/quizzes/028_kitchen_task_assessment_form--quizzes.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -826,8 +826,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
-    <col width="38" customWidth="1" min="2" max="2"/>
-    <col width="38" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -855,12 +855,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'basic'}</t>
+          <t>basic</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Basic'}</t>
+          <t>Basic</t>
         </is>
       </c>
     </row>
@@ -872,12 +872,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'intermediate'}</t>
+          <t>intermediate</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Intermediate'}</t>
+          <t>Intermediate</t>
         </is>
       </c>
     </row>
@@ -889,12 +889,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'advanced'}</t>
+          <t>advanced</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Advanced'}</t>
+          <t>Advanced</t>
         </is>
       </c>
     </row>
@@ -906,12 +906,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'chef'}</t>
+          <t>chef</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Chef'}</t>
+          <t>Chef</t>
         </is>
       </c>
     </row>
@@ -923,12 +923,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'cook'}</t>
+          <t>cook</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Cook'}</t>
+          <t>Cook</t>
         </is>
       </c>
     </row>
@@ -940,12 +940,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'restaurateur'}</t>
+          <t>restaurateur</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Restaurateur'}</t>
+          <t>Restaurateur</t>
         </is>
       </c>
     </row>
@@ -957,12 +957,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'knife_skills'}</t>
+          <t>knife_skills</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'knife skills'}</t>
+          <t>knife skills</t>
         </is>
       </c>
     </row>
@@ -974,12 +974,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'knife_safety'}</t>
+          <t>knife_safety</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'knife safety'}</t>
+          <t>knife safety</t>
         </is>
       </c>
     </row>
@@ -991,12 +991,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'knife_handling'}</t>
+          <t>knife_handling</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'knife handling'}</t>
+          <t>knife handling</t>
         </is>
       </c>
     </row>
@@ -1008,12 +1008,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'prep'}</t>
+          <t>prep</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'prep'}</t>
+          <t>prep</t>
         </is>
       </c>
     </row>
@@ -1025,12 +1025,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'cooking'}</t>
+          <t>cooking</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'cooking'}</t>
+          <t>cooking</t>
         </is>
       </c>
     </row>
@@ -1042,12 +1042,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'food_safety'}</t>
+          <t>food_safety</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'food safety'}</t>
+          <t>food safety</t>
         </is>
       </c>
     </row>
@@ -1059,12 +1059,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'knives'}</t>
+          <t>knives</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'knives'}</t>
+          <t>knives</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'pots_and_pans'}</t>
+          <t>pots_and_pans</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'pots and pans'}</t>
+          <t>pots and pans</t>
         </is>
       </c>
     </row>
@@ -1093,12 +1093,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'appliances'}</t>
+          <t>appliances</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'appliances'}</t>
+          <t>appliances</t>
         </is>
       </c>
     </row>
@@ -1110,12 +1110,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'layout'}</t>
+          <t>layout</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'layout'}</t>
+          <t>layout</t>
         </is>
       </c>
     </row>
@@ -1127,12 +1127,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'organization'}</t>
+          <t>organization</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'organization'}</t>
+          <t>organization</t>
         </is>
       </c>
     </row>
@@ -1144,12 +1144,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'efficiency'}</t>
+          <t>efficiency</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'efficiency'}</t>
+          <t>efficiency</t>
         </is>
       </c>
     </row>
@@ -1161,12 +1161,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'presentation'}</t>
+          <t>presentation</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'presentation'}</t>
+          <t>presentation</t>
         </is>
       </c>
     </row>
@@ -1178,12 +1178,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'taste'}</t>
+          <t>taste</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'taste'}</t>
+          <t>taste</t>
         </is>
       </c>
     </row>
@@ -1195,12 +1195,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'consistency'}</t>
+          <t>consistency</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'consistency'}</t>
+          <t>consistency</t>
         </is>
       </c>
     </row>
@@ -1212,12 +1212,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'communication'}</t>
+          <t>communication</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'communication'}</t>
+          <t>communication</t>
         </is>
       </c>
     </row>
@@ -1229,12 +1229,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'cooperation'}</t>
+          <t>cooperation</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'cooperation'}</t>
+          <t>cooperation</t>
         </is>
       </c>
     </row>
@@ -1246,12 +1246,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'leadership'}</t>
+          <t>leadership</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'leadership'}</t>
+          <t>leadership</t>
         </is>
       </c>
     </row>
@@ -1263,12 +1263,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'scheduling'}</t>
+          <t>scheduling</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'scheduling'}</t>
+          <t>scheduling</t>
         </is>
       </c>
     </row>
@@ -1280,12 +1280,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'prioritization'}</t>
+          <t>prioritization</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'prioritization'}</t>
+          <t>prioritization</t>
         </is>
       </c>
     </row>
@@ -1297,12 +1297,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'pacing'}</t>
+          <t>pacing</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'pacing'}</t>
+          <t>pacing</t>
         </is>
       </c>
     </row>
